--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Lab Observation: Cytopathology, ResourceType Observation</t>
+    <t>This StructureDefinition contains the maps for VistA CYTOPATHOLOGY (file 63.09) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1239,7 +1239,7 @@
     <t>704319004 |Inherent in|</t>
   </si>
   <si>
-    <t>1618: reference from CYTOPATHOLOGY - CYTOPATH ACC # (#63.09-.06)</t>
+    <t>+: reference from CYTOPATHOLOGY - CYTOPATH ACC # (#63.09-.06)</t>
   </si>
   <si>
     <t>Observation.device</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3082" uniqueCount="551">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab</t>
+    <t>http://va.gov/fhir/StructureDefinition/LabObservationObservation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -659,7 +659,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
+    <t>http://va.gov/fhir/ValueSet/VFDiagnosticReportLabStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -712,6 +712,188 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category.id</t>
+  </si>
+  <si>
+    <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>843: fixed value = laboratory</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Observation.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.category:Laboratory</t>
@@ -803,6 +985,30 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN
+Micro.AntibioticSensitivityComment.LRDFN
+Pathology.Autopsy.LRDFN
+Micro.BacteriologyReports.LRDFN
+Pathology.CytoOrganTissueFunction.StaffIEN
+Micro.MicroAntibioticLevel.LRDFN
+Micro.MicroAudit.LRDFN
+Micro.Microbiology.LRDFN
+Micro.MicroOrderedTest.LRDFN
+Micro.MicroSterilityResults.LRDFN
+Micro.MycobacteriologyReports.LRDFN
+Micro.Mycology.LRDFN
+Micro.MycologyReports.LRDFN
+Micro.Parasitology.LRDFN
+Micro.ParasitologyReports.LRDFN
+Micro.ParasitologyStage.LRDFN
+SStaff.SMicroOrderedTest.LRDFN
+Micro.Virology.LRDFN
+Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1893,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR61"/>
+  <dimension ref="A1:AT72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1919,7 +2125,7 @@
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="14.109375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1938,6 +2144,8 @@
     <col min="42" max="42" width="30.0703125" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="61.78515625" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="206.16015625" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="61.78515625" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="206.16015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2065,6 +2273,12 @@
       <c r="AR1" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT1" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2191,6 +2405,12 @@
       <c r="AR2" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -2315,6 +2535,12 @@
       <c r="AR3" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT3" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -2441,6 +2667,12 @@
       <c r="AR4" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT4" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -2567,6 +2799,12 @@
       <c r="AR5" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS5" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT5" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -2693,6 +2931,12 @@
       <c r="AR6" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT6" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -2819,6 +3063,12 @@
       <c r="AR7" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT7" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -2945,6 +3195,12 @@
       <c r="AR8" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT8" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -3073,6 +3329,12 @@
       <c r="AR9" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT9" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -3199,6 +3461,12 @@
       <c r="AR10" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS10" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT10" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -3323,6 +3591,12 @@
       <c r="AR11" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS11" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
@@ -3449,6 +3723,12 @@
       <c r="AR12" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS12" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT12" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
@@ -3577,6 +3857,12 @@
       <c r="AR13" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS13" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT13" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
@@ -3705,6 +3991,12 @@
       <c r="AR14" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS14" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT14" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
@@ -3833,6 +4125,12 @@
       <c r="AR15" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS15" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT15" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
@@ -3959,6 +4257,12 @@
       <c r="AR16" t="s" s="2">
         <v>166</v>
       </c>
+      <c r="AS16" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT16" t="s" s="2">
+        <v>166</v>
+      </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
@@ -4083,6 +4387,12 @@
       <c r="AR17" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS17" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT17" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
@@ -4209,6 +4519,12 @@
       <c r="AR18" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS18" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT18" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
@@ -4335,6 +4651,12 @@
       <c r="AR19" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS19" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT19" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
@@ -4461,6 +4783,12 @@
       <c r="AR20" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS20" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT20" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
@@ -4587,6 +4915,12 @@
       <c r="AR21" t="s" s="2">
         <v>212</v>
       </c>
+      <c r="AS21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AT21" t="s" s="2">
+        <v>212</v>
+      </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
@@ -4713,29 +5047,33 @@
       <c r="AR22" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS22" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT22" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>40</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>50</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>40</v>
@@ -4744,20 +5082,16 @@
         <v>40</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>118</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>40</v>
       </c>
@@ -4766,7 +5100,7 @@
         <v>40</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>40</v>
@@ -4781,13 +5115,13 @@
         <v>40</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>218</v>
+        <v>40</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>219</v>
+        <v>40</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>40</v>
@@ -4805,19 +5139,19 @@
         <v>40</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>40</v>
@@ -4829,10 +5163,10 @@
         <v>40</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>221</v>
+        <v>121</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>222</v>
+        <v>40</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>40</v>
@@ -4841,51 +5175,55 @@
         <v>40</v>
       </c>
       <c r="AR23" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT23" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>123</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>40</v>
       </c>
@@ -4909,75 +5247,81 @@
         <v>40</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>233</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>127</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>235</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>237</v>
+        <v>121</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>238</v>
+        <v>40</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>240</v>
+        <v>40</v>
+      </c>
+      <c r="AS24" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT24" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4985,13 +5329,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>40</v>
@@ -5000,19 +5344,19 @@
         <v>51</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>40</v>
@@ -5061,13 +5405,13 @@
         <v>40</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>40</v>
@@ -5076,19 +5420,19 @@
         <v>62</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>40</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>40</v>
@@ -5097,15 +5441,21 @@
         <v>40</v>
       </c>
       <c r="AR25" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS25" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT25" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5116,7 +5466,7 @@
         <v>38</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>40</v>
@@ -5125,20 +5475,18 @@
         <v>40</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>40</v>
@@ -5187,19 +5535,19 @@
         <v>40</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>40</v>
@@ -5208,13 +5556,13 @@
         <v>40</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>256</v>
+        <v>121</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>40</v>
@@ -5223,26 +5571,32 @@
         <v>40</v>
       </c>
       <c r="AR26" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS26" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT26" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>258</v>
+        <v>95</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>40</v>
@@ -5251,23 +5605,21 @@
         <v>40</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>96</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>97</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>123</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>40</v>
       </c>
@@ -5303,46 +5655,46 @@
         <v>40</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>127</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>40</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>40</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>40</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>40</v>
@@ -5351,19 +5703,25 @@
         <v>40</v>
       </c>
       <c r="AR27" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT27" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>269</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5373,7 +5731,7 @@
         <v>50</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>40</v>
@@ -5382,19 +5740,19 @@
         <v>51</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>270</v>
+        <v>64</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>40</v>
@@ -5431,17 +5789,19 @@
         <v>40</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -5450,25 +5810,25 @@
         <v>50</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>276</v>
+        <v>40</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>277</v>
+        <v>62</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>278</v>
+        <v>40</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>281</v>
+        <v>40</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>40</v>
@@ -5477,21 +5837,25 @@
         <v>40</v>
       </c>
       <c r="AR28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT28" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>269</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5501,7 +5865,7 @@
         <v>50</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>40</v>
@@ -5510,20 +5874,18 @@
         <v>51</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>284</v>
+        <v>117</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>40</v>
       </c>
@@ -5571,7 +5933,7 @@
         <v>40</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -5580,42 +5942,48 @@
         <v>50</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>276</v>
+        <v>40</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>277</v>
+        <v>62</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>278</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>281</v>
+        <v>40</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>285</v>
+        <v>40</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>286</v>
+        <v>40</v>
+      </c>
+      <c r="AS29" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT29" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5638,18 +6006,18 @@
         <v>51</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>40</v>
       </c>
@@ -5697,7 +6065,7 @@
         <v>40</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
@@ -5718,30 +6086,36 @@
         <v>40</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>294</v>
+        <v>40</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>295</v>
+        <v>40</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>296</v>
+        <v>258</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT30" t="s" s="2">
+        <v>258</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5752,7 +6126,7 @@
         <v>38</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>40</v>
@@ -5764,17 +6138,17 @@
         <v>51</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>298</v>
+        <v>117</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>40</v>
@@ -5823,13 +6197,13 @@
         <v>40</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>40</v>
@@ -5838,36 +6212,42 @@
         <v>62</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>302</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>304</v>
+        <v>265</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>305</v>
+        <v>40</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>306</v>
+        <v>40</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>307</v>
+        <v>40</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT31" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5881,7 +6261,7 @@
         <v>50</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>40</v>
@@ -5890,19 +6270,19 @@
         <v>51</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>40</v>
@@ -5939,17 +6319,19 @@
         <v>40</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -5958,46 +6340,50 @@
         <v>50</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>314</v>
+        <v>40</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>315</v>
+        <v>62</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>316</v>
+        <v>40</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>317</v>
+        <v>273</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>318</v>
+        <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>319</v>
+        <v>40</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR32" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT32" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>40</v>
       </c>
@@ -6009,7 +6395,7 @@
         <v>50</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>40</v>
@@ -6021,16 +6407,16 @@
         <v>117</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>40</v>
@@ -6079,7 +6465,7 @@
         <v>40</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -6088,50 +6474,58 @@
         <v>50</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>314</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>315</v>
+        <v>62</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>316</v>
+        <v>40</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>282</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>319</v>
+        <v>40</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>322</v>
+        <v>40</v>
+      </c>
+      <c r="AS33" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT33" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>40</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>50</v>
@@ -6149,16 +6543,16 @@
         <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>214</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>215</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>326</v>
+        <v>216</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>327</v>
+        <v>217</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>40</v>
@@ -6168,7 +6562,7 @@
         <v>40</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>40</v>
+        <v>285</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>40</v>
@@ -6183,11 +6577,13 @@
         <v>40</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>328</v>
+        <v>219</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>40</v>
@@ -6205,16 +6601,16 @@
         <v>40</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>213</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>329</v>
+        <v>40</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>62</v>
@@ -6226,13 +6622,13 @@
         <v>40</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>330</v>
+        <v>221</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>40</v>
@@ -6241,50 +6637,56 @@
         <v>40</v>
       </c>
       <c r="AR34" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS34" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT34" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>332</v>
+        <v>287</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>289</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>335</v>
+        <v>290</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>336</v>
+        <v>291</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>40</v>
@@ -6312,10 +6714,10 @@
         <v>144</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>338</v>
+        <v>293</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>40</v>
@@ -6333,13 +6735,13 @@
         <v>40</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>40</v>
@@ -6348,36 +6750,42 @@
         <v>62</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>40</v>
+        <v>294</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>341</v>
+        <v>297</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>40</v>
+        <v>298</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>342</v>
+        <v>299</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>40</v>
+        <v>300</v>
+      </c>
+      <c r="AS35" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT35" t="s" s="2">
+        <v>300</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6385,34 +6793,34 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>304</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>347</v>
+        <v>305</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>348</v>
+        <v>306</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>40</v>
@@ -6461,13 +6869,13 @@
         <v>40</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>40</v>
@@ -6476,36 +6884,42 @@
         <v>62</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>40</v>
+        <v>307</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>40</v>
+        <v>310</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>352</v>
+        <v>312</v>
+      </c>
+      <c r="AS36" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AT36" t="s" s="2">
+        <v>312</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6516,7 +6930,7 @@
         <v>38</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>40</v>
@@ -6525,19 +6939,19 @@
         <v>40</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>139</v>
+        <v>314</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>315</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>356</v>
+        <v>317</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6563,13 +6977,13 @@
         <v>40</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>357</v>
+        <v>40</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>358</v>
+        <v>40</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>359</v>
+        <v>40</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>40</v>
@@ -6587,13 +7001,13 @@
         <v>40</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>40</v>
@@ -6605,37 +7019,43 @@
         <v>40</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>360</v>
+        <v>40</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>361</v>
+        <v>296</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>40</v>
+        <v>310</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>363</v>
+        <v>40</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR37" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS37" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT37" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6651,22 +7071,22 @@
         <v>40</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>139</v>
+        <v>321</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>368</v>
+        <v>325</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>40</v>
@@ -6691,13 +7111,13 @@
         <v>40</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>357</v>
+        <v>40</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>369</v>
+        <v>40</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>370</v>
+        <v>40</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>40</v>
@@ -6715,7 +7135,7 @@
         <v>40</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
@@ -6730,19 +7150,19 @@
         <v>62</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>40</v>
+        <v>326</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>371</v>
+        <v>327</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>40</v>
+        <v>329</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>40</v>
@@ -6751,19 +7171,25 @@
         <v>40</v>
       </c>
       <c r="AR38" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS38" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT38" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>373</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>40</v>
+        <v>331</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6773,27 +7199,29 @@
         <v>50</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>374</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>375</v>
+        <v>333</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>40</v>
       </c>
@@ -6829,19 +7257,17 @@
         <v>40</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>373</v>
+        <v>330</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>38</v>
@@ -6850,46 +7276,54 @@
         <v>50</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>40</v>
+        <v>338</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>62</v>
+        <v>339</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>378</v>
+        <v>40</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>379</v>
+        <v>341</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>380</v>
+        <v>342</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>40</v>
+        <v>343</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>381</v>
+        <v>40</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>382</v>
+        <v>40</v>
+      </c>
+      <c r="AS39" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT39" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>40</v>
+        <v>331</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6899,27 +7333,29 @@
         <v>50</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>384</v>
+        <v>346</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>40</v>
       </c>
@@ -6967,7 +7403,7 @@
         <v>40</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>383</v>
+        <v>330</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>38</v>
@@ -6976,42 +7412,48 @@
         <v>50</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>40</v>
+        <v>338</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>62</v>
+        <v>339</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>388</v>
+        <v>40</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>389</v>
+        <v>341</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>40</v>
+        <v>343</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>391</v>
+        <v>40</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>40</v>
+        <v>347</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>40</v>
+        <v>348</v>
+      </c>
+      <c r="AS40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AT40" t="s" s="2">
+        <v>348</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7022,7 +7464,7 @@
         <v>38</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>40</v>
@@ -7031,23 +7473,21 @@
         <v>40</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>395</v>
+        <v>352</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>40</v>
       </c>
@@ -7095,19 +7535,19 @@
         <v>40</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>398</v>
+        <v>62</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>40</v>
@@ -7116,30 +7556,36 @@
         <v>40</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>399</v>
+        <v>354</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>40</v>
+        <v>356</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>40</v>
+        <v>357</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>40</v>
+        <v>358</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AT41" t="s" s="2">
+        <v>358</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7150,7 +7596,7 @@
         <v>38</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>40</v>
@@ -7159,19 +7605,21 @@
         <v>40</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>117</v>
+        <v>360</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>118</v>
+        <v>361</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>40</v>
       </c>
@@ -7219,85 +7667,93 @@
         <v>40</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>120</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>40</v>
+        <v>364</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>40</v>
+        <v>365</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>121</v>
+        <v>366</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>40</v>
+        <v>367</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>40</v>
+        <v>368</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>40</v>
+        <v>369</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AT42" t="s" s="2">
+        <v>369</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>96</v>
+        <v>371</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>97</v>
+        <v>372</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>123</v>
+        <v>373</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>40</v>
       </c>
@@ -7333,98 +7789,104 @@
         <v>40</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>127</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>40</v>
+        <v>376</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>377</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>40</v>
+        <v>378</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>40</v>
+        <v>379</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>121</v>
+        <v>380</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>40</v>
+        <v>381</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR43" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS43" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT43" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>404</v>
+        <v>40</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>51</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>99</v>
+        <v>374</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>105</v>
+        <v>375</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>40</v>
@@ -7473,51 +7935,57 @@
         <v>40</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>40</v>
+        <v>376</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>377</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>40</v>
+        <v>378</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>40</v>
+        <v>379</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>93</v>
+        <v>380</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>40</v>
+        <v>381</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>40</v>
+        <v>384</v>
+      </c>
+      <c r="AS44" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT44" t="s" s="2">
+        <v>384</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7531,7 +7999,7 @@
         <v>50</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>40</v>
@@ -7540,16 +8008,20 @@
         <v>40</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>409</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>40</v>
       </c>
@@ -7573,13 +8045,11 @@
         <v>40</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>40</v>
+        <v>390</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>40</v>
@@ -7597,7 +8067,7 @@
         <v>40</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -7606,7 +8076,7 @@
         <v>50</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>62</v>
@@ -7618,10 +8088,10 @@
         <v>40</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>413</v>
+        <v>93</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>40</v>
@@ -7633,26 +8103,32 @@
         <v>40</v>
       </c>
       <c r="AR45" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS45" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT45" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>40</v>
+        <v>394</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>40</v>
@@ -7664,16 +8140,20 @@
         <v>40</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>409</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>40</v>
       </c>
@@ -7697,13 +8177,13 @@
         <v>40</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>40</v>
+        <v>399</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>40</v>
@@ -7721,16 +8201,16 @@
         <v>40</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>412</v>
+        <v>40</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>62</v>
@@ -7739,33 +8219,39 @@
         <v>40</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>40</v>
+        <v>401</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>40</v>
+        <v>404</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR46" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT46" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7776,7 +8262,7 @@
         <v>38</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>40</v>
@@ -7788,19 +8274,19 @@
         <v>40</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>406</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>40</v>
@@ -7825,13 +8311,13 @@
         <v>40</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>424</v>
+        <v>40</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>425</v>
+        <v>40</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>40</v>
@@ -7849,13 +8335,13 @@
         <v>40</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>40</v>
@@ -7867,13 +8353,13 @@
         <v>40</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>426</v>
+        <v>40</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>341</v>
+        <v>412</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>40</v>
@@ -7882,18 +8368,24 @@
         <v>40</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>40</v>
+        <v>413</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>40</v>
+        <v>414</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AT47" t="s" s="2">
+        <v>414</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7904,7 +8396,7 @@
         <v>38</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>40</v>
@@ -7919,17 +8411,15 @@
         <v>139</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>40</v>
       </c>
@@ -7953,13 +8443,13 @@
         <v>40</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>357</v>
+        <v>419</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>40</v>
@@ -7977,13 +8467,13 @@
         <v>40</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>40</v>
@@ -7995,33 +8485,39 @@
         <v>40</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>341</v>
+        <v>424</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>40</v>
+        <v>425</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR48" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS48" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT48" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8044,17 +8540,19 @@
         <v>40</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>436</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>40</v>
@@ -8079,13 +8577,13 @@
         <v>40</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>40</v>
+        <v>419</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>40</v>
+        <v>431</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>40</v>
+        <v>432</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>40</v>
@@ -8103,7 +8601,7 @@
         <v>40</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>38</v>
@@ -8124,10 +8622,10 @@
         <v>40</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>40</v>
+        <v>433</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>40</v>
@@ -8139,15 +8637,21 @@
         <v>40</v>
       </c>
       <c r="AR49" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS49" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT49" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8170,15 +8674,17 @@
         <v>40</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>117</v>
+        <v>436</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>40</v>
@@ -8227,7 +8733,7 @@
         <v>40</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>38</v>
@@ -8245,25 +8751,31 @@
         <v>40</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>40</v>
+        <v>440</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AO50" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>40</v>
+      <c r="AS50" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT50" t="s" s="2">
+        <v>444</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8282,7 +8794,7 @@
         <v>38</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>40</v>
@@ -8291,7 +8803,7 @@
         <v>40</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>446</v>
@@ -8359,7 +8871,7 @@
         <v>38</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>40</v>
@@ -8371,33 +8883,39 @@
         <v>40</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>40</v>
+        <v>450</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>40</v>
+        <v>453</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR51" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS51" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT51" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8417,21 +8935,23 @@
         <v>40</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>40</v>
       </c>
@@ -8479,7 +8999,7 @@
         <v>40</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>38</v>
@@ -8491,7 +9011,7 @@
         <v>40</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>62</v>
+        <v>460</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>40</v>
@@ -8500,10 +9020,10 @@
         <v>40</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>40</v>
@@ -8515,15 +9035,21 @@
         <v>40</v>
       </c>
       <c r="AR52" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS52" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT52" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8534,7 +9060,7 @@
         <v>38</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>40</v>
@@ -8543,23 +9069,19 @@
         <v>40</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>393</v>
+        <v>117</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>118</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>40</v>
       </c>
@@ -8607,19 +9129,19 @@
         <v>40</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>458</v>
+        <v>120</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>40</v>
@@ -8628,10 +9150,10 @@
         <v>40</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>463</v>
+        <v>40</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>121</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>40</v>
@@ -8643,26 +9165,32 @@
         <v>40</v>
       </c>
       <c r="AR53" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS53" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT53" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>40</v>
@@ -8674,15 +9202,17 @@
         <v>40</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>40</v>
@@ -8731,19 +9261,19 @@
         <v>40</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>40</v>
@@ -8767,19 +9297,25 @@
         <v>40</v>
       </c>
       <c r="AR54" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS54" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT54" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>95</v>
+        <v>466</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8792,24 +9328,26 @@
         <v>40</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>96</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>97</v>
+        <v>467</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>123</v>
+        <v>468</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>40</v>
       </c>
@@ -8857,7 +9395,7 @@
         <v>40</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>127</v>
+        <v>469</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
@@ -8881,7 +9419,7 @@
         <v>40</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>40</v>
@@ -8893,51 +9431,53 @@
         <v>40</v>
       </c>
       <c r="AR55" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS55" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT55" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>404</v>
+        <v>40</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>40</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>96</v>
+        <v>471</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>405</v>
+        <v>472</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>40</v>
       </c>
@@ -8985,19 +9525,19 @@
         <v>40</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>470</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>40</v>
+        <v>474</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>40</v>
@@ -9006,10 +9546,10 @@
         <v>40</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>40</v>
+        <v>475</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>93</v>
+        <v>476</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>40</v>
@@ -9021,15 +9561,21 @@
         <v>40</v>
       </c>
       <c r="AR56" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS56" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT56" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9037,7 +9583,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>50</v>
@@ -9049,23 +9595,19 @@
         <v>40</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>471</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>40</v>
       </c>
@@ -9089,13 +9631,13 @@
         <v>40</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>357</v>
+        <v>40</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>472</v>
+        <v>40</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>233</v>
+        <v>40</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>40</v>
@@ -9113,16 +9655,16 @@
         <v>40</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>50</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>40</v>
+        <v>474</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>62</v>
@@ -9131,16 +9673,16 @@
         <v>40</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>473</v>
+        <v>40</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>236</v>
+        <v>475</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>237</v>
+        <v>480</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>238</v>
+        <v>40</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>40</v>
@@ -9149,15 +9691,21 @@
         <v>40</v>
       </c>
       <c r="AR57" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS57" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT57" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9177,22 +9725,22 @@
         <v>40</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>309</v>
+        <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>313</v>
+        <v>485</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>40</v>
@@ -9217,13 +9765,13 @@
         <v>40</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>40</v>
+        <v>486</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>40</v>
+        <v>487</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>40</v>
@@ -9241,7 +9789,7 @@
         <v>40</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>38</v>
@@ -9259,33 +9807,39 @@
         <v>40</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>317</v>
+        <v>489</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>318</v>
+        <v>403</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>319</v>
+        <v>40</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR58" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS58" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT58" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9296,7 +9850,7 @@
         <v>38</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>40</v>
@@ -9311,16 +9865,16 @@
         <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>327</v>
+        <v>494</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>40</v>
@@ -9345,13 +9899,13 @@
         <v>40</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>144</v>
+        <v>419</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>328</v>
+        <v>496</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>40</v>
@@ -9369,16 +9923,16 @@
         <v>40</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>484</v>
+        <v>40</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>62</v>
@@ -9387,13 +9941,13 @@
         <v>40</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>40</v>
+        <v>488</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>93</v>
+        <v>489</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>330</v>
+        <v>403</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>40</v>
@@ -9405,26 +9959,32 @@
         <v>40</v>
       </c>
       <c r="AR59" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS59" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT59" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>332</v>
+        <v>40</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>40</v>
@@ -9436,19 +9996,17 @@
         <v>40</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>139</v>
+        <v>498</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>333</v>
+        <v>499</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>336</v>
+        <v>501</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>40</v>
@@ -9473,13 +10031,13 @@
         <v>40</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>337</v>
+        <v>40</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>338</v>
+        <v>40</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>40</v>
@@ -9497,13 +10055,13 @@
         <v>40</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>40</v>
@@ -9515,33 +10073,39 @@
         <v>40</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>339</v>
+        <v>40</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>341</v>
+        <v>502</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>342</v>
+        <v>40</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR60" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS60" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT60" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9552,7 +10116,7 @@
         <v>38</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>40</v>
@@ -9564,20 +10128,16 @@
         <v>40</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>40</v>
       </c>
@@ -9625,13 +10185,13 @@
         <v>40</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>40</v>
@@ -9646,26 +10206,1496 @@
         <v>40</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT61" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT62" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT63" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT64" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT65" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT66" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT67" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT68" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT69" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT70" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="Y71" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="Z71" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AO61" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AR61" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT71" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT72" t="s" s="2">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR61">
+  <autoFilter ref="A1:AT72">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9675,7 +11705,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="595">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -809,10 +809,10 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>1494: terminologyMaps using VF_DiagnosticReportLabStatus on CYTOPATHOLOGY - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.09-.35 &gt; 63.51-10)</t>
+  </si>
+  <si>
     <t>Pathology.CytoOrderedTest.DispositionLabCodeIEN</t>
-  </si>
-  <si>
-    <t>1494: terminologyMaps using VF_DiagnosticReportLabStatus on CYTOPATHOLOGY - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.09-.35 &gt; 63.51-10)</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -944,6 +944,10 @@
   </si>
   <si>
     <t>Coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-8:843: fixed value "laboratory" {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1117,6 +1121,9 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN
@@ -1140,9 +1147,6 @@
 Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
     <t>Observation.focus</t>
   </si>
   <si>
@@ -1252,6 +1256,9 @@
   <si>
     <t xml:space="preserve">dateTime
 </t>
+  </si>
+  <si>
+    <t>1452: source value from CYTOPATHOLOGY - DATE/TIME SPECIMEN TAKEN (#63.09-.01)</t>
   </si>
   <si>
     <t>Pathology.CytoDelayedReportComment.SpecimenTakenDateTime
@@ -1278,9 +1285,6 @@
 Pathology.CytoTIUReference.SpecimenTakenDateTime</t>
   </si>
   <si>
-    <t>1452: source value from CYTOPATHOLOGY - DATE/TIME SPECIMEN TAKEN (#63.09-.01)</t>
-  </si>
-  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -1306,12 +1310,12 @@
     <t>FiveWs.recorded</t>
   </si>
   <si>
+    <t>1486: source value from CYTOPATHOLOGY - DATE REPORT COMPLETED (#63.09-.03)</t>
+  </si>
+  <si>
     <t>Pathology.Cytopathology.ReportCompletedDateTime</t>
   </si>
   <si>
-    <t>1486: source value from CYTOPATHOLOGY - DATE REPORT COMPLETED (#63.09-.03)</t>
-  </si>
-  <si>
     <t>Observation.performer</t>
   </si>
   <si>
@@ -1336,10 +1340,10 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
+    <t>1466: reference from CYTOPATHOLOGY - RELEASING SITE (#63.09-.345)</t>
+  </si>
+  <si>
     <t>Pathology.Cytopathology.ReleasingInstitutionIEN</t>
-  </si>
-  <si>
-    <t>1466: reference from CYTOPATHOLOGY - RELEASING SITE (#63.09-.345)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1478,10 +1482,10 @@
     <t>subjectOf.observationEvent[code="annotation"].value</t>
   </si>
   <si>
+    <t>1462: source value from CYTOPATHOLOGY - COMMENT &gt; COMMENT - COMMENT (#63.09-.99 &gt; 63.908-.01)</t>
+  </si>
+  <si>
     <t>Pathology.CytoReportComment.CytopathologyComment</t>
-  </si>
-  <si>
-    <t>1462: source value from CYTOPATHOLOGY - COMMENT &gt; COMMENT - COMMENT (#63.09-.99 &gt; 63.908-.01)</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -2271,10 +2275,10 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="61.78515625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="206.16015625" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="61.78515625" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="206.16015625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="206.16015625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="61.78515625" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="206.16015625" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="61.78515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4521,16 +4525,16 @@
         <v>84</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AR17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AS17" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AT17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -6346,7 +6350,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6355,10 +6359,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6367,24 +6371,24 @@
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="AS31" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AT31" t="s" s="2">
-        <v>302</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6410,14 +6414,14 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6466,7 +6470,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6487,10 +6491,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6513,10 +6517,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6539,19 +6543,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6600,7 +6604,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6621,10 +6625,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6647,10 +6651,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6676,16 +6680,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6734,7 +6738,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6755,10 +6759,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6781,13 +6785,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>257</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6831,7 +6835,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -6917,14 +6921,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6946,16 +6950,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6983,10 +6987,10 @@
         <v>188</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -7004,7 +7008,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>94</v>
@@ -7019,42 +7023,42 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>344</v>
+        <v>84</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AT36" t="s" s="2">
-        <v>344</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7077,19 +7081,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7138,7 +7142,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7153,42 +7157,42 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AR37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AS37" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AS37" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AT37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7211,16 +7215,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7270,7 +7274,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7291,13 +7295,13 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>84</v>
@@ -7317,14 +7321,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7343,19 +7347,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7404,7 +7408,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7419,19 +7423,19 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
@@ -7451,14 +7455,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7477,19 +7481,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7526,7 +7530,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7536,7 +7540,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7545,25 +7549,25 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>84</v>
@@ -7583,16 +7587,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7611,19 +7615,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7672,7 +7676,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7681,48 +7685,48 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AR41" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AS41" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AS41" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AT41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7745,16 +7749,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7804,7 +7808,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7825,36 +7829,36 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AR42" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AS42" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AS42" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AT42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7880,14 +7884,14 @@
         <v>219</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7936,7 +7940,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7951,42 +7955,42 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AR43" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AS43" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AS43" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="AT43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8009,19 +8013,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8058,7 +8062,7 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -8068,7 +8072,7 @@
         <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8077,28 +8081,28 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8115,13 +8119,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -8146,16 +8150,16 @@
         <v>161</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8204,7 +8208,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8213,48 +8217,48 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
+        <v>428</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>427</v>
+        <v>84</v>
       </c>
       <c r="AS45" t="s" s="2">
-        <v>84</v>
+        <v>428</v>
       </c>
       <c r="AT45" t="s" s="2">
-        <v>427</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8280,16 +8284,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8318,7 +8322,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8336,7 +8340,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8345,7 +8349,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -8360,7 +8364,7 @@
         <v>137</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8383,14 +8387,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8412,16 +8416,16 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8449,10 +8453,10 @@
         <v>188</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8470,7 +8474,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8488,19 +8492,19 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8517,10 +8521,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8543,19 +8547,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8604,7 +8608,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8625,10 +8629,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8637,24 +8641,24 @@
         <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AR48" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AS48" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AS48" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="AT48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8680,13 +8684,13 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8712,13 +8716,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8736,7 +8740,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8754,19 +8758,19 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8783,10 +8787,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8812,16 +8816,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8846,13 +8850,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8870,7 +8874,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8891,10 +8895,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8917,10 +8921,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8943,16 +8947,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9002,7 +9006,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9020,39 +9024,39 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>84</v>
+        <v>488</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>487</v>
+        <v>84</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>84</v>
+        <v>488</v>
       </c>
       <c r="AT51" t="s" s="2">
-        <v>487</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9075,16 +9079,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9134,7 +9138,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9152,19 +9156,19 @@
         <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9181,10 +9185,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9207,19 +9211,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9268,7 +9272,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9280,7 +9284,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -9289,10 +9293,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -9315,10 +9319,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9445,10 +9449,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9577,14 +9581,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9606,10 +9610,10 @@
         <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -9664,7 +9668,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9711,10 +9715,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9737,13 +9741,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9794,7 +9798,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9803,7 +9807,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9815,10 +9819,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9841,10 +9845,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9867,13 +9871,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9924,7 +9928,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9933,7 +9937,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9945,10 +9949,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9971,10 +9975,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10000,16 +10004,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10037,10 +10041,10 @@
         <v>118</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -10058,7 +10062,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10076,13 +10080,13 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
@@ -10105,10 +10109,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10134,16 +10138,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10168,13 +10172,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -10192,7 +10196,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10210,13 +10214,13 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -10239,10 +10243,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10265,17 +10269,17 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10324,7 +10328,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10348,7 +10352,7 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10371,10 +10375,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10400,10 +10404,10 @@
         <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10454,7 +10458,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10475,10 +10479,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10501,10 +10505,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10527,16 +10531,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10586,7 +10590,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10607,10 +10611,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10633,10 +10637,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10659,16 +10663,16 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10718,7 +10722,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10739,10 +10743,10 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10765,10 +10769,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10791,19 +10795,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10852,7 +10856,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10873,10 +10877,10 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10899,10 +10903,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11029,10 +11033,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11161,14 +11165,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -11190,10 +11194,10 @@
         <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
@@ -11248,7 +11252,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11295,10 +11299,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11324,16 +11328,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11358,13 +11362,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11382,7 +11386,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -11400,16 +11404,16 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>84</v>
@@ -11429,10 +11433,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11455,19 +11459,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11516,7 +11520,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11534,19 +11538,19 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11563,10 +11567,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11592,16 +11596,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11629,10 +11633,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11650,7 +11654,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11659,7 +11663,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11674,7 +11678,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11697,14 +11701,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11726,16 +11730,16 @@
         <v>183</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11763,10 +11767,10 @@
         <v>188</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11784,7 +11788,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11802,19 +11806,19 @@
         <v>84</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11831,10 +11835,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11860,16 +11864,16 @@
         <v>85</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11918,7 +11922,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11939,10 +11943,10 @@
         <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -947,7 +947,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-8:843: fixed value "laboratory" {null}</t>
+inv-9:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="596">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -947,7 +947,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-9:843: fixed value = laboratory {null}</t>
+inv-10:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1577,7 +1577,10 @@
     <t>704319004 |Inherent in|</t>
   </si>
   <si>
-    <t>+: reference from CYTOPATHOLOGY - CYTOPATH ACC # (#63.09-.06)</t>
+    <t>1657: reference from CYTOPATHOLOGY - CYTOPATH ACC # (#63.09-.06)</t>
+  </si>
+  <si>
+    <t>Pathology.Cytopathology.CytopathAccessionNumber</t>
   </si>
   <si>
     <t>Observation.device</t>
@@ -9042,21 +9045,21 @@
         <v>488</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>488</v>
       </c>
       <c r="AT51" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9079,16 +9082,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9138,7 +9141,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9156,19 +9159,19 @@
         <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9185,10 +9188,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9211,19 +9214,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9272,7 +9275,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9284,7 +9287,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -9293,10 +9296,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -9319,10 +9322,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9449,10 +9452,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9581,14 +9584,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9610,10 +9613,10 @@
         <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -9668,7 +9671,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9715,10 +9718,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9741,13 +9744,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9798,7 +9801,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9807,7 +9810,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9819,10 +9822,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9845,10 +9848,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9871,13 +9874,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9928,7 +9931,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9937,7 +9940,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9949,10 +9952,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9975,10 +9978,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10004,16 +10007,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10041,10 +10044,10 @@
         <v>118</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -10062,7 +10065,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10080,10 +10083,10 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>447</v>
@@ -10109,10 +10112,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10138,16 +10141,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10175,10 +10178,10 @@
         <v>463</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -10196,7 +10199,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10214,10 +10217,10 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>447</v>
@@ -10243,10 +10246,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10269,17 +10272,17 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10328,7 +10331,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10352,7 +10355,7 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10375,10 +10378,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10404,10 +10407,10 @@
         <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10458,7 +10461,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10479,10 +10482,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10505,10 +10508,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10531,16 +10534,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10590,7 +10593,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10611,10 +10614,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10637,10 +10640,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10663,16 +10666,16 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10722,7 +10725,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10743,10 +10746,10 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10769,10 +10772,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10795,19 +10798,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10856,7 +10859,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10877,10 +10880,10 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10903,10 +10906,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11033,10 +11036,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11165,14 +11168,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -11194,10 +11197,10 @@
         <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
@@ -11252,7 +11255,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11299,10 +11302,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11328,13 +11331,13 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>336</v>
@@ -11365,7 +11368,7 @@
         <v>463</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>338</v>
@@ -11386,7 +11389,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -11404,7 +11407,7 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>341</v>
@@ -11433,10 +11436,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11462,13 +11465,13 @@
         <v>415</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>419</v>
@@ -11520,7 +11523,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11538,7 +11541,7 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>423</v>
@@ -11567,10 +11570,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11596,13 +11599,13 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>433</v>
@@ -11633,7 +11636,7 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>434</v>
@@ -11654,7 +11657,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11663,7 +11666,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11701,10 +11704,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11788,7 +11791,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11835,10 +11838,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11864,16 +11867,16 @@
         <v>85</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11922,7 +11925,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11943,10 +11946,10 @@
         <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA CYTOPATHOLOGY (file 63.09) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file CYTOPATHOLOGY (#63.09) to LabObservationObservation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation: Cytopathology {Observation}</t>
+    <t>Lab Observation: Cytopathology Observation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file CYTOPATHOLOGY (#63.09) to LabObservationObservation</t>
+    <t>This StructureDefinition contains the maps for VistA file CYTOPATHOLOGY (#63.09) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/StructureDefinition/LabObservationObservation</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -844,192 +844,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t>Observation.category.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-10:843: fixed value = laboratory {null}</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>843: fixed value = laboratory</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Observation.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.category:Laboratory</t>
@@ -1121,30 +935,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Pathology.Autopsy.LRDFN
-Micro.BacteriologyReports.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-SStaff.SMicroOrderedTest.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -2234,7 +2024,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT73"/>
+  <dimension ref="A1:AR62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -2280,8 +2070,6 @@
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="206.16015625" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="61.78515625" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="206.16015625" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="61.78515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2417,12 +2205,6 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
-      <c r="AS1" t="s" s="1">
-        <v>79</v>
-      </c>
-      <c r="AT1" t="s" s="1">
-        <v>80</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2549,12 +2331,6 @@
       <c r="AR2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT2" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -2681,12 +2457,6 @@
       <c r="AR3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS3" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT3" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -2811,12 +2581,6 @@
       <c r="AR4" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT4" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -2943,12 +2707,6 @@
       <c r="AR5" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT5" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -3075,12 +2833,6 @@
       <c r="AR6" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT6" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -3207,12 +2959,6 @@
       <c r="AR7" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT7" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -3339,12 +3085,6 @@
       <c r="AR8" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT8" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -3471,12 +3211,6 @@
       <c r="AR9" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT9" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -3605,12 +3339,6 @@
       <c r="AR10" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT10" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -3737,12 +3465,6 @@
       <c r="AR11" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT11" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
@@ -3867,12 +3589,6 @@
       <c r="AR12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT12" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
@@ -3999,12 +3715,6 @@
       <c r="AR13" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT13" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
@@ -4133,12 +3843,6 @@
       <c r="AR14" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT14" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
@@ -4267,12 +3971,6 @@
       <c r="AR15" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT15" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
@@ -4401,12 +4099,6 @@
       <c r="AR16" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT16" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
@@ -4427,7 +4119,7 @@
         <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>84</v>
@@ -4531,12 +4223,6 @@
         <v>210</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS17" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AT17" t="s" s="2">
         <v>84</v>
       </c>
     </row>
@@ -4663,12 +4349,6 @@
       <c r="AR18" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT18" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
@@ -4795,12 +4475,6 @@
       <c r="AR19" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT19" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
@@ -4927,12 +4601,6 @@
       <c r="AR20" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT20" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
@@ -5059,12 +4727,6 @@
       <c r="AR21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT21" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
@@ -5191,12 +4853,6 @@
       <c r="AR22" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AS22" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AT22" t="s" s="2">
-        <v>256</v>
-      </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
@@ -5323,33 +4979,29 @@
       <c r="AR23" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT23" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -5358,16 +5010,20 @@
         <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
       </c>
@@ -5376,7 +5032,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>269</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5391,13 +5047,13 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5415,19 +5071,19 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>164</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -5439,10 +5095,10 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>84</v>
@@ -5451,55 +5107,51 @@
         <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT24" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>139</v>
+        <v>271</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>141</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
       </c>
@@ -5523,81 +5175,75 @@
         <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>84</v>
+        <v>277</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT25" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5605,13 +5251,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>84</v>
@@ -5620,19 +5266,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5681,13 +5327,13 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>84</v>
@@ -5696,19 +5342,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>84</v>
@@ -5717,21 +5363,15 @@
         <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT26" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5742,7 +5382,7 @@
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>84</v>
@@ -5751,18 +5391,20 @@
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>161</v>
+        <v>296</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>297</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5811,19 +5453,19 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>295</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5832,13 +5474,13 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>84</v>
@@ -5847,32 +5489,26 @@
         <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT27" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>139</v>
+        <v>302</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>84</v>
@@ -5881,21 +5517,23 @@
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>140</v>
+        <v>303</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>141</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5931,46 +5569,46 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>309</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>84</v>
@@ -5979,25 +5617,19 @@
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT28" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -6007,7 +5639,7 @@
         <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -6016,19 +5648,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>314</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -6065,19 +5697,17 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6086,25 +5716,25 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>321</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>287</v>
+        <v>324</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>84</v>
@@ -6113,25 +5743,21 @@
         <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT29" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -6141,7 +5767,7 @@
         <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
@@ -6150,18 +5776,20 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>328</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -6209,7 +5837,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6218,48 +5846,42 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>321</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>329</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT30" t="s" s="2">
-        <v>84</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6273,7 +5895,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6282,18 +5904,18 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>332</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6341,7 +5963,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>331</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6353,7 +5975,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>300</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6362,36 +5984,30 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>84</v>
+        <v>338</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS31" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AT31" t="s" s="2">
-        <v>84</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6402,10 +6018,10 @@
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
@@ -6414,17 +6030,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6473,13 +6089,13 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
@@ -6488,42 +6104,36 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT32" t="s" s="2">
-        <v>84</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6537,7 +6147,7 @@
         <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>84</v>
@@ -6546,19 +6156,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>312</v>
+        <v>352</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6595,19 +6205,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6616,50 +6224,46 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>358</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>319</v>
+        <v>361</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT33" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>363</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6671,7 +6275,7 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>84</v>
@@ -6683,16 +6287,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6741,7 +6345,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6750,58 +6354,50 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>358</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>365</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT34" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
@@ -6819,16 +6415,16 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>258</v>
+        <v>367</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>259</v>
+        <v>368</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>260</v>
+        <v>369</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>261</v>
+        <v>370</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6838,7 +6434,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>330</v>
+        <v>84</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -6853,13 +6449,11 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>263</v>
+        <v>371</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6877,16 +6471,16 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>257</v>
+        <v>366</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -6898,13 +6492,13 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>265</v>
+        <v>373</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>266</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
@@ -6913,56 +6507,50 @@
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT35" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>332</v>
+        <v>375</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>376</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6990,10 +6578,10 @@
         <v>188</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>337</v>
+        <v>380</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>338</v>
+        <v>381</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -7011,13 +6599,13 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
@@ -7026,42 +6614,36 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AT36" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7069,10 +6651,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>95</v>
@@ -7081,22 +6663,22 @@
         <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>347</v>
+        <v>387</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>351</v>
+        <v>391</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7145,13 +6727,13 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>84</v>
@@ -7160,42 +6742,36 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>352</v>
+        <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>355</v>
+        <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AS37" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AT37" t="s" s="2">
-        <v>357</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7206,7 +6782,7 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -7215,19 +6791,19 @@
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>359</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>361</v>
+        <v>398</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7253,13 +6829,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -7277,13 +6853,13 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
@@ -7295,43 +6871,37 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>355</v>
+        <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>84</v>
+        <v>406</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT38" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>365</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7347,22 +6917,22 @@
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>366</v>
+        <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7387,13 +6957,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>84</v>
+        <v>413</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7411,7 +6981,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7426,19 +6996,19 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>371</v>
+        <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
@@ -7447,25 +7017,19 @@
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT39" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7481,23 +7045,21 @@
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>378</v>
+        <v>418</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7533,17 +7095,19 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AC40" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7552,54 +7116,46 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>384</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>388</v>
+        <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>84</v>
+        <v>424</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>425</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT40" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7609,29 +7165,27 @@
         <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>378</v>
+        <v>429</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>379</v>
+        <v>430</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7679,7 +7233,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>375</v>
+        <v>427</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7688,48 +7242,42 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>384</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>387</v>
+        <v>434</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>388</v>
+        <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>392</v>
+        <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AS41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AT41" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7740,7 +7288,7 @@
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>84</v>
@@ -7749,21 +7297,23 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7811,19 +7361,19 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>442</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7832,36 +7382,30 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>399</v>
+        <v>443</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>400</v>
+        <v>444</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>402</v>
+        <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AS42" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AT42" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>404</v>
+        <v>445</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>404</v>
+        <v>445</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7872,7 +7416,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
@@ -7881,21 +7425,19 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>405</v>
+        <v>162</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>406</v>
+        <v>163</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7943,93 +7485,85 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>404</v>
+        <v>164</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>410</v>
+        <v>165</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>411</v>
+        <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>412</v>
+        <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AS43" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AT43" t="s" s="2">
-        <v>413</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>415</v>
+        <v>140</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>417</v>
+        <v>167</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -8065,104 +7599,98 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>414</v>
+        <v>171</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>421</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>422</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>424</v>
+        <v>165</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>425</v>
+        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT44" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I45" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>418</v>
+        <v>143</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>419</v>
+        <v>149</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8211,57 +7739,51 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>421</v>
+        <v>145</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>422</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>424</v>
+        <v>137</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>425</v>
+        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS45" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AT45" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8275,7 +7797,7 @@
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
@@ -8284,20 +7806,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>183</v>
+        <v>453</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8321,11 +7839,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8343,7 +7863,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8352,7 +7872,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -8364,10 +7884,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>137</v>
+        <v>457</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8379,32 +7899,26 @@
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT46" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>438</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -8416,20 +7930,16 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>183</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8453,13 +7963,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8477,16 +7987,16 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>84</v>
+        <v>456</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -8495,39 +8005,33 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT47" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8538,7 +8042,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -8550,19 +8054,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>450</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8587,13 +8091,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8611,13 +8115,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8629,13 +8133,13 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8644,24 +8148,18 @@
         <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>457</v>
+        <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AS48" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AT48" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8672,7 +8170,7 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
@@ -8687,15 +8185,17 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8719,13 +8219,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>463</v>
+        <v>400</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8743,13 +8243,13 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
@@ -8761,39 +8261,33 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>468</v>
+        <v>384</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT49" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8816,19 +8310,17 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>183</v>
+        <v>480</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8853,13 +8345,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>463</v>
+        <v>84</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8877,7 +8369,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8898,10 +8390,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8913,21 +8405,15 @@
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT50" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8950,17 +8436,15 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>480</v>
+        <v>161</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9009,7 +8493,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9027,39 +8511,33 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>484</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>487</v>
+        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AS51" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AT51" t="s" s="2">
-        <v>489</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9070,7 +8548,7 @@
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -9079,19 +8557,19 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9141,13 +8619,13 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
@@ -9159,39 +8637,33 @@
         <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>498</v>
+        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT52" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9211,23 +8683,21 @@
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>504</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -9275,7 +8745,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9287,7 +8757,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>505</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -9296,10 +8766,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -9311,21 +8781,15 @@
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT53" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9336,7 +8800,7 @@
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
@@ -9345,19 +8809,23 @@
         <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>437</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>162</v>
+        <v>503</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9405,19 +8873,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>164</v>
+        <v>502</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -9426,10 +8894,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>84</v>
+        <v>507</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>165</v>
+        <v>508</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -9441,12 +8909,6 @@
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT54" t="s" s="2">
         <v>84</v>
       </c>
     </row>
@@ -9459,14 +8921,14 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9478,17 +8940,15 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9537,19 +8997,19 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -9573,12 +9033,6 @@
         <v>84</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT55" t="s" s="2">
         <v>84</v>
       </c>
     </row>
@@ -9591,7 +9045,7 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>511</v>
+        <v>139</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9604,26 +9058,24 @@
         <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>512</v>
+        <v>141</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>513</v>
+        <v>167</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O56" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9671,7 +9123,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>514</v>
+        <v>171</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9695,7 +9147,7 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
@@ -9707,53 +9159,51 @@
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT56" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>516</v>
+        <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>517</v>
+        <v>449</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9801,19 +9251,19 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>515</v>
+        <v>451</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>519</v>
+        <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9822,10 +9272,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>520</v>
+        <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>521</v>
+        <v>137</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9837,21 +9287,15 @@
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT57" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9859,7 +9303,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>94</v>
@@ -9871,19 +9315,23 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>516</v>
+        <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9907,13 +9355,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>84</v>
+        <v>516</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>84</v>
+        <v>277</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9931,16 +9379,16 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>519</v>
+        <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9949,16 +9397,16 @@
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>84</v>
+        <v>517</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>520</v>
+        <v>280</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>525</v>
+        <v>281</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>84</v>
@@ -9967,21 +9415,15 @@
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT58" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10001,22 +9443,22 @@
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>183</v>
+        <v>352</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>530</v>
+        <v>356</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10041,13 +9483,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>531</v>
+        <v>84</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>532</v>
+        <v>84</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -10065,7 +9507,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10083,39 +9525,33 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>534</v>
+        <v>360</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>447</v>
+        <v>361</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT59" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10126,7 +9562,7 @@
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
@@ -10141,16 +9577,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>539</v>
+        <v>370</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10175,13 +9611,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>463</v>
+        <v>188</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>541</v>
+        <v>371</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -10199,16 +9635,16 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -10217,13 +9653,13 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>533</v>
+        <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>534</v>
+        <v>137</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>447</v>
+        <v>373</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -10235,32 +9671,26 @@
         <v>84</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT60" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -10272,17 +9702,19 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>543</v>
+        <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>544</v>
+        <v>376</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>546</v>
+        <v>379</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10307,13 +9739,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -10331,13 +9763,13 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
@@ -10349,39 +9781,33 @@
         <v>84</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>84</v>
+        <v>382</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>547</v>
+        <v>384</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT61" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10392,7 +9818,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -10404,16 +9830,20 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -10461,13 +9891,13 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
@@ -10482,10 +9912,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>520</v>
+        <v>443</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>551</v>
+        <v>444</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10497,1481 +9927,11 @@
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT62" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT63" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT64" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT65" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT66" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT67" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT68" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT69" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT70" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT71" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT72" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT73" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT73">
+  <autoFilter ref="A1:AR62">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11981,7 +9941,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI72">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="464">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -733,6 +736,27 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN
+Micro.AntibioticSensitivityComment.LRDFN
+Micro.BacteriologyReports.LRDFN
+Micro.MicroAntibioticLevel.LRDFN
+Micro.MicroAudit.LRDFN
+Micro.Microbiology.LRDFN
+Micro.MicroOrderedTest.LRDFN
+Micro.MicroSterilityResults.LRDFN
+Micro.MycobacteriologyReports.LRDFN
+Micro.Mycology.LRDFN
+Micro.MycologyReports.LRDFN
+Micro.Parasitology.LRDFN
+Micro.ParasitologyReports.LRDFN
+Micro.ParasitologyStage.LRDFN
+Micro.Virology.LRDFN
+Micro.VirologyReports.LRDFN
+Pathology.Autopsy.LRDFN
+Pathology.CytoOrganTissueFunction.StaffIEN
+SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1786,7 +1810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR52"/>
+  <dimension ref="A1:AS52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1826,12 +1850,13 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="42.265625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1967,6 +1992,9 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
+      <c r="AS1" t="s" s="1">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1977,106 +2005,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>90</v>
@@ -2088,1135 +2116,1162 @@
         <v>92</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AR2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS2" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS3" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS4" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS5" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS6" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="AR7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS7" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS8" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS9" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS10" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
@@ -3225,370 +3280,379 @@
         <v>159</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
+      </c>
+      <c r="AS11" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS12" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>177</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS13" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>186</v>
@@ -3603,376 +3667,385 @@
         <v>189</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>84</v>
+        <v>190</v>
+      </c>
+      <c r="AS14" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AE15" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="AS15" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="AS16" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>216</v>
@@ -3988,3921 +4061,4014 @@
       </c>
       <c r="AR17" t="s" s="2">
         <v>220</v>
+      </c>
+      <c r="AS17" t="s" s="2">
+        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
+      </c>
+      <c r="AS18" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
+      </c>
+      <c r="AS19" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>84</v>
+        <v>248</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
+      </c>
+      <c r="AS20" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
+      </c>
+      <c r="AS21" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
+      </c>
+      <c r="AS22" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>85</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>277</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
+      </c>
+      <c r="AS24" t="s" s="2">
+        <v>293</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS25" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH26" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>308</v>
+        <v>85</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>311</v>
+        <v>85</v>
+      </c>
+      <c r="AS26" t="s" s="2">
+        <v>313</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH27" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>318</v>
+        <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>327</v>
+        <v>85</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>330</v>
+        <v>85</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>332</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>338</v>
+        <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>84</v>
+        <v>341</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS29" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>345</v>
+        <v>85</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>348</v>
+        <v>85</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>350</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>354</v>
+        <v>85</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>358</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>357</v>
+        <v>85</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>359</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>365</v>
+        <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>372</v>
+        <v>85</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS33" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>372</v>
+        <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS34" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS35" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>386</v>
+        <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS36" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS37" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>85</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>310</v>
+        <v>402</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS38" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF39" t="s" s="2">
+      <c r="AI39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AP39" t="s" s="2">
-        <v>310</v>
+        <v>402</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS39" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>413</v>
+        <v>85</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS40" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>386</v>
+        <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>419</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>423</v>
+        <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF43" t="s" s="2">
+      <c r="AI43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS43" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>84</v>
+        <v>439</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS44" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>372</v>
+        <v>85</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS45" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>372</v>
+        <v>85</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>446</v>
+        <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>217</v>
+        <v>448</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>218</v>
@@ -7911,523 +8077,538 @@
         <v>219</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
+        <v>220</v>
+      </c>
+      <c r="AS48" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>451</v>
+        <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>289</v>
+        <v>453</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
+      </c>
+      <c r="AS49" t="s" s="2">
+        <v>293</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS50" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH51" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>308</v>
+        <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>311</v>
+        <v>85</v>
+      </c>
+      <c r="AS51" t="s" s="2">
+        <v>313</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH52" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>365</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS52" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR52">
+  <autoFilter ref="A1:AS52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -716,7 +713,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -736,27 +733,6 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Micro.BacteriologyReports.LRDFN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN
-Pathology.Autopsy.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1810,7 +1786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS52"/>
+  <dimension ref="A1:AR52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1850,13 +1826,12 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="42.265625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1992,9 +1967,6 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
-      <c r="AS1" t="s" s="1">
-        <v>81</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2005,106 +1977,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G2" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="M2" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="N2" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>90</v>
@@ -2116,1162 +2088,1135 @@
         <v>92</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="AR2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR3" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>107</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="AG7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AQ7" t="s" s="2">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="AR7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AG8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AQ8" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF9" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>146</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR9" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>150</v>
-      </c>
       <c r="P10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH10" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR10" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G11" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G11" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH11" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
@@ -3280,379 +3225,370 @@
         <v>159</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AS11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G12" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH12" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH13" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>177</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H14" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="I14" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="O14" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="P14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>186</v>
@@ -3667,385 +3603,376 @@
         <v>189</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AS14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="P15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="T15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AF15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AS15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="D16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H16" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="P16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>199</v>
-      </c>
       <c r="AA16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH16" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AS16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H17" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G17" t="s" s="2">
+      <c r="I17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="P17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>216</v>
@@ -4061,4014 +3988,3921 @@
       </c>
       <c r="AR17" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AS17" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G18" t="s" s="2">
+      <c r="I18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="O18" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="P18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AQ18" t="s" s="2">
-        <v>233</v>
-      </c>
       <c r="AR18" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AS18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G19" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH19" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AS19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="P20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>85</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AO20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AQ20" t="s" s="2">
-        <v>250</v>
-      </c>
       <c r="AR20" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AS20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="P21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AJ21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AK21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AO21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AQ21" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="AR21" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AS21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K22" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>85</v>
+        <v>268</v>
       </c>
       <c r="AP22" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AQ22" t="s" s="2">
-        <v>271</v>
-      </c>
       <c r="AR22" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AS22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH23" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>85</v>
+        <v>276</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AQ23" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="AR23" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AS23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N24" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="P24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS24" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H25" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="P25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="AQ25" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G26" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="P26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS26" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G27" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>319</v>
-      </c>
       <c r="P27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH27" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH27" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>85</v>
+        <v>318</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>321</v>
+        <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AA28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS28" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="P29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AA29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AQ29" t="s" s="2">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>85</v>
+        <v>345</v>
       </c>
       <c r="AO30" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AP30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS30" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>85</v>
+        <v>354</v>
       </c>
       <c r="AO31" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AP31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR31" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AR31" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS31" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="P32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH32" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AQ32" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G34" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>142</v>
-      </c>
       <c r="M34" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH34" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G35" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH35" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AQ36" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>85</v>
+        <v>386</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="P38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AP38" t="s" s="2">
-        <v>402</v>
+        <v>310</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G39" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G39" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="P39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AG39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH39" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>402</v>
+        <v>310</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>85</v>
+        <v>413</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>415</v>
+        <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>85</v>
+        <v>386</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>419</v>
+        <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH42" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>426</v>
+        <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH43" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>432</v>
+        <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="P44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH44" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>85</v>
+        <v>436</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G46" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G46" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>142</v>
-      </c>
       <c r="M46" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH46" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G47" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G47" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH47" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>85</v>
+        <v>446</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>448</v>
+        <v>217</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>218</v>
@@ -8077,538 +7911,523 @@
         <v>219</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AS48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H49" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>85</v>
+        <v>451</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>453</v>
+        <v>289</v>
       </c>
       <c r="AP49" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS49" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Z50" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AA50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="AQ50" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G51" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G51" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N51" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="P51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AA51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS51" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G52" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G52" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH52" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH52" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>85</v>
+        <v>365</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS52">
+  <autoFilter ref="A1:AR52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -957,6 +957,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -4982,7 +4985,7 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>299</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
@@ -4997,7 +5000,7 @@
         <v>137</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5008,14 +5011,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5037,16 +5040,16 @@
         <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5074,10 +5077,10 @@
         <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>84</v>
@@ -5095,7 +5098,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5119,27 +5122,27 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5162,19 +5165,19 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5223,7 +5226,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5250,10 +5253,10 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5264,10 +5267,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5293,13 +5296,13 @@
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5325,13 +5328,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5349,7 +5352,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5373,27 +5376,27 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5419,16 +5422,16 @@
         <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5453,13 +5456,13 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5477,7 +5480,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5504,10 +5507,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5518,10 +5521,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5544,16 +5547,16 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5603,7 +5606,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5627,27 +5630,27 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5670,16 +5673,16 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5729,7 +5732,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5753,27 +5756,27 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5796,19 +5799,19 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -5857,7 +5860,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5869,7 +5872,7 @@
         <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>84</v>
@@ -5884,10 +5887,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -5898,10 +5901,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5924,13 +5927,13 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5981,7 +5984,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6011,7 +6014,7 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6022,10 +6025,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6054,7 +6057,7 @@
         <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>143</v>
@@ -6107,7 +6110,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6137,7 +6140,7 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6148,14 +6151,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6177,10 +6180,10 @@
         <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>143</v>
@@ -6235,7 +6238,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6276,10 +6279,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6302,13 +6305,13 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6359,7 +6362,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6368,7 +6371,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6386,10 +6389,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6400,10 +6403,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6426,13 +6429,13 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6483,7 +6486,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6492,7 +6495,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6510,10 +6513,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6524,10 +6527,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6553,16 +6556,16 @@
         <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6590,10 +6593,10 @@
         <v>118</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6611,7 +6614,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6635,13 +6638,13 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6652,10 +6655,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6681,16 +6684,16 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6715,13 +6718,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6739,7 +6742,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6763,13 +6766,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6780,10 +6783,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6806,17 +6809,17 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -6865,7 +6868,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6895,7 +6898,7 @@
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6906,10 +6909,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6932,13 +6935,13 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6989,7 +6992,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7016,10 +7019,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7030,10 +7033,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7056,16 +7059,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7115,7 +7118,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7142,10 +7145,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7156,10 +7159,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7182,16 +7185,16 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7241,7 +7244,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7268,10 +7271,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7282,10 +7285,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7308,19 +7311,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7369,7 +7372,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7396,10 +7399,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7410,10 +7413,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7436,13 +7439,13 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7493,7 +7496,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7523,7 +7526,7 @@
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7534,10 +7537,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7566,7 +7569,7 @@
         <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
@@ -7619,7 +7622,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7649,7 +7652,7 @@
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7660,14 +7663,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7689,10 +7692,10 @@
         <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>143</v>
@@ -7747,7 +7750,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7788,10 +7791,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7817,13 +7820,13 @@
         <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>211</v>
@@ -7851,10 +7854,10 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>214</v>
@@ -7875,7 +7878,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>94</v>
@@ -7899,7 +7902,7 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>217</v>
@@ -7916,10 +7919,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7945,13 +7948,13 @@
         <v>281</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>285</v>
@@ -8003,7 +8006,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8027,7 +8030,7 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>289</v>
@@ -8044,10 +8047,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8073,13 +8076,13 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>296</v>
@@ -8110,7 +8113,7 @@
         <v>212</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>297</v>
@@ -8131,7 +8134,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8140,7 +8143,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8161,7 +8164,7 @@
         <v>137</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8172,14 +8175,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8201,16 +8204,16 @@
         <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8238,10 +8241,10 @@
         <v>212</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8259,7 +8262,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8283,27 +8286,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8329,16 +8332,16 @@
         <v>85</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8387,7 +8390,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8414,10 +8417,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -959,7 +959,7 @@
 us-core-2</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2031: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -733,6 +736,9 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
+  </si>
+  <si>
+    <t>demographics.lrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1789,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR52"/>
+  <dimension ref="A1:AS52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1829,12 +1835,13 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1970,6 +1977,9 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
+      <c r="AS1" t="s" s="1">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1980,106 +1990,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>90</v>
@@ -2091,1135 +2101,1162 @@
         <v>92</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AR2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS2" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS3" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS4" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS5" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS6" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="AR7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS7" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS8" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS9" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS10" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
@@ -3228,370 +3265,379 @@
         <v>159</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
+      </c>
+      <c r="AS11" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS12" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>177</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS13" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>186</v>
@@ -3606,376 +3652,385 @@
         <v>189</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>84</v>
+        <v>190</v>
+      </c>
+      <c r="AS14" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AE15" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="AS15" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="AS16" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>216</v>
@@ -3991,3921 +4046,4014 @@
       </c>
       <c r="AR17" t="s" s="2">
         <v>220</v>
+      </c>
+      <c r="AS17" t="s" s="2">
+        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
+      </c>
+      <c r="AS18" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
+      </c>
+      <c r="AS19" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>84</v>
+        <v>248</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
+      </c>
+      <c r="AS20" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
+      </c>
+      <c r="AS21" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
+      </c>
+      <c r="AS22" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>85</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>277</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
+      </c>
+      <c r="AS24" t="s" s="2">
+        <v>293</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS25" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH26" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>312</v>
+        <v>85</v>
+      </c>
+      <c r="AS26" t="s" s="2">
+        <v>314</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH27" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>319</v>
+        <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>328</v>
+        <v>85</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>332</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>331</v>
+        <v>85</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>333</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>339</v>
+        <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>84</v>
+        <v>342</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS29" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>346</v>
+        <v>85</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>350</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>349</v>
+        <v>85</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>351</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>355</v>
+        <v>85</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>358</v>
+        <v>85</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>360</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>366</v>
+        <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS33" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS34" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS35" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>387</v>
+        <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS36" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>394</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS37" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>311</v>
+        <v>403</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS38" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF39" t="s" s="2">
+      <c r="AI39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AP39" t="s" s="2">
-        <v>311</v>
+        <v>403</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS39" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>414</v>
+        <v>85</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS40" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>387</v>
+        <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>424</v>
+        <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>427</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF43" t="s" s="2">
+      <c r="AI43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>433</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS43" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>437</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS44" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS45" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>217</v>
+        <v>449</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>218</v>
@@ -7914,523 +8062,538 @@
         <v>219</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
+        <v>220</v>
+      </c>
+      <c r="AS48" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>289</v>
+        <v>454</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
+      </c>
+      <c r="AS49" t="s" s="2">
+        <v>293</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS50" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH51" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>312</v>
+        <v>85</v>
+      </c>
+      <c r="AS51" t="s" s="2">
+        <v>314</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH52" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>366</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS52" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR52">
+  <autoFilter ref="A1:AS52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,7 +738,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1836,7 +1836,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,8 +738,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,7 +738,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$56</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="482">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -595,6 +595,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-status</t>
+  </si>
+  <si>
+    <t>2153: target not supported</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -695,6 +698,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t>2154: target not supported</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -830,6 +836,10 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">us-core-1
 </t>
   </si>
@@ -850,6 +860,19 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>2155: target not supported</t>
+  </si>
+  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -942,6 +965,41 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>2156: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>2157: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>2158: target not supported</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1180,10 +1238,6 @@
   </si>
   <si>
     <t>Observation.referenceRange.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Unique id for inter-element referencing</t>
@@ -1795,12 +1849,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS52"/>
+  <dimension ref="A1:AS56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3631,7 +3685,7 @@
         <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>85</v>
@@ -3640,19 +3694,19 @@
         <v>85</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AS14" t="s" s="2">
         <v>85</v>
@@ -3660,10 +3714,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3686,19 +3740,19 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>85</v>
@@ -3708,7 +3762,7 @@
         <v>85</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>85</v>
@@ -3726,26 +3780,26 @@
         <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -3760,7 +3814,7 @@
         <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>85</v>
@@ -3778,10 +3832,10 @@
         <v>85</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AS15" t="s" s="2">
         <v>85</v>
@@ -3789,13 +3843,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>85</v>
@@ -3817,19 +3871,19 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>85</v>
@@ -3839,7 +3893,7 @@
         <v>85</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>85</v>
@@ -3857,10 +3911,10 @@
         <v>119</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>85</v>
@@ -3878,7 +3932,7 @@
         <v>85</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -3911,10 +3965,10 @@
         <v>85</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AS16" t="s" s="2">
         <v>85</v>
@@ -3922,14 +3976,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3948,19 +4002,19 @@
         <v>96</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>85</v>
@@ -3985,13 +4039,13 @@
         <v>85</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>85</v>
@@ -4009,7 +4063,7 @@
         <v>85</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>95</v>
@@ -4024,7 +4078,7 @@
         <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>85</v>
@@ -4033,30 +4087,30 @@
         <v>85</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AS17" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4079,19 +4133,19 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>85</v>
@@ -4140,7 +4194,7 @@
         <v>85</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
@@ -4155,28 +4209,28 @@
         <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AS18" t="s" s="2">
         <v>85</v>
@@ -4184,10 +4238,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4210,16 +4264,16 @@
         <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4269,7 +4323,7 @@
         <v>85</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -4299,13 +4353,13 @@
         <v>85</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AS19" t="s" s="2">
         <v>85</v>
@@ -4313,14 +4367,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4339,19 +4393,19 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>85</v>
@@ -4400,7 +4454,7 @@
         <v>85</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4424,19 +4478,19 @@
         <v>85</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS20" t="s" s="2">
         <v>85</v>
@@ -4444,14 +4498,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4470,19 +4524,19 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>85</v>
@@ -4519,19 +4573,17 @@
         <v>85</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -4540,10 +4592,10 @@
         <v>95</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>85</v>
@@ -4555,19 +4607,19 @@
         <v>85</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>85</v>
@@ -4575,14 +4627,16 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4592,7 +4646,7 @@
         <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>85</v>
@@ -4601,18 +4655,20 @@
         <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>85</v>
       </c>
@@ -4660,7 +4716,7 @@
         <v>85</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4669,13 +4725,13 @@
         <v>95</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>85</v>
+        <v>262</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>107</v>
+        <v>263</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>85</v>
+        <v>271</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>85</v>
@@ -4684,19 +4740,19 @@
         <v>85</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>85</v>
+        <v>264</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -4704,10 +4760,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4718,7 +4774,7 @@
         <v>83</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>85</v>
@@ -4730,18 +4786,18 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>277</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>85</v>
       </c>
@@ -4789,13 +4845,13 @@
         <v>85</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>85</v>
@@ -4813,19 +4869,19 @@
         <v>85</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
+      <c r="AR23" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -4833,10 +4889,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4847,10 +4903,10 @@
         <v>83</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>85</v>
@@ -4859,19 +4915,17 @@
         <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -4920,54 +4974,54 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AS24" t="s" s="2">
-        <v>293</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4987,22 +5041,22 @@
         <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>290</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5027,29 +5081,29 @@
         <v>85</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>299</v>
+        <v>85</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5058,80 +5112,82 @@
         <v>95</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AR25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS25" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS25" t="s" s="2">
-        <v>85</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="D26" t="s" s="2">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>192</v>
+        <v>303</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>85</v>
@@ -5156,13 +5212,13 @@
         <v>85</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>213</v>
+        <v>85</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>85</v>
@@ -5180,22 +5236,22 @@
         <v>85</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>85</v>
+        <v>295</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>107</v>
+        <v>296</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>85</v>
+        <v>304</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>85</v>
@@ -5207,29 +5263,31 @@
         <v>85</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>314</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>85</v>
       </c>
@@ -5238,31 +5296,31 @@
         <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>316</v>
+        <v>193</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>85</v>
@@ -5311,22 +5369,22 @@
         <v>85</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>85</v>
+        <v>295</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>107</v>
+        <v>296</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>85</v>
+        <v>307</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>85</v>
@@ -5338,29 +5396,31 @@
         <v>85</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>85</v>
+        <v>297</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS27" t="s" s="2">
-        <v>85</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>85</v>
       </c>
@@ -5372,27 +5432,29 @@
         <v>95</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>310</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
       </c>
@@ -5416,13 +5478,13 @@
         <v>85</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>327</v>
+        <v>85</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>328</v>
+        <v>85</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>329</v>
+        <v>85</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>85</v>
@@ -5440,7 +5502,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5449,13 +5511,13 @@
         <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>85</v>
+        <v>295</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>107</v>
+        <v>296</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>85</v>
+        <v>311</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -5467,27 +5529,27 @@
         <v>85</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS28" t="s" s="2">
-        <v>333</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5501,7 +5563,7 @@
         <v>95</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>85</v>
@@ -5510,19 +5572,19 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>85</v>
@@ -5547,13 +5609,11 @@
         <v>85</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>85</v>
@@ -5571,7 +5631,7 @@
         <v>85</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5580,13 +5640,13 @@
         <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>85</v>
+        <v>318</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>85</v>
@@ -5601,10 +5661,10 @@
         <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>341</v>
+        <v>138</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>85</v>
@@ -5615,21 +5675,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>85</v>
+        <v>322</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>85</v>
@@ -5641,18 +5701,20 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>344</v>
+        <v>193</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>85</v>
       </c>
@@ -5676,13 +5738,13 @@
         <v>85</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>85</v>
+        <v>327</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>85</v>
+        <v>328</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>85</v>
@@ -5700,13 +5762,13 @@
         <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>85</v>
@@ -5727,27 +5789,27 @@
         <v>85</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS30" t="s" s="2">
-        <v>351</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5758,7 +5820,7 @@
         <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>85</v>
@@ -5770,18 +5832,20 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
       </c>
@@ -5829,13 +5893,13 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>85</v>
@@ -5856,27 +5920,27 @@
         <v>85</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>357</v>
+        <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS31" t="s" s="2">
-        <v>360</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5887,7 +5951,7 @@
         <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>85</v>
@@ -5899,20 +5963,18 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>362</v>
+        <v>193</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>85</v>
       </c>
@@ -5936,13 +5998,13 @@
         <v>85</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>85</v>
+        <v>345</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>85</v>
+        <v>346</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>85</v>
+        <v>347</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>85</v>
@@ -5960,19 +6022,19 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>367</v>
+        <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>85</v>
@@ -5987,27 +6049,27 @@
         <v>85</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>85</v>
+        <v>348</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS32" t="s" s="2">
-        <v>85</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6030,16 +6092,20 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>371</v>
+        <v>193</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
       </c>
@@ -6063,13 +6129,13 @@
         <v>85</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>85</v>
+        <v>345</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>85</v>
+        <v>357</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>85</v>
+        <v>358</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>85</v>
@@ -6087,7 +6153,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6099,7 +6165,7 @@
         <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>85</v>
@@ -6117,10 +6183,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>85</v>
+        <v>359</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6131,21 +6197,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>85</v>
@@ -6157,16 +6223,16 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>141</v>
+        <v>362</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>142</v>
+        <v>363</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>144</v>
+        <v>365</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6216,19 +6282,19 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>85</v>
@@ -6243,63 +6309,61 @@
         <v>85</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>85</v>
+        <v>366</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>85</v>
+        <v>367</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS34" t="s" s="2">
-        <v>85</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>380</v>
+        <v>85</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>141</v>
+        <v>371</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>85</v>
       </c>
@@ -6347,19 +6411,19 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>85</v>
@@ -6374,27 +6438,27 @@
         <v>85</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>85</v>
+        <v>376</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>138</v>
+        <v>377</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS35" t="s" s="2">
-        <v>85</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6405,7 +6469,7 @@
         <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>85</v>
@@ -6417,16 +6481,20 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
       </c>
@@ -6474,19 +6542,19 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>388</v>
+        <v>85</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>107</v>
+        <v>385</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>85</v>
@@ -6504,10 +6572,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -6518,10 +6586,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6544,13 +6612,13 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>385</v>
+        <v>310</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6610,10 +6678,10 @@
         <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>388</v>
+        <v>85</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>85</v>
@@ -6631,10 +6699,10 @@
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>389</v>
+        <v>85</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -6645,21 +6713,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>85</v>
@@ -6671,20 +6739,18 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>396</v>
+        <v>142</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>85</v>
       </c>
@@ -6708,13 +6774,13 @@
         <v>85</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>401</v>
+        <v>85</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>85</v>
@@ -6738,13 +6804,13 @@
         <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>85</v>
@@ -6759,13 +6825,13 @@
         <v>85</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>402</v>
+        <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>403</v>
+        <v>85</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>313</v>
+        <v>392</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>85</v>
@@ -6776,14 +6842,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>85</v>
+        <v>397</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6796,25 +6862,25 @@
         <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>407</v>
+        <v>144</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -6839,13 +6905,13 @@
         <v>85</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>327</v>
+        <v>85</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>409</v>
+        <v>85</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>410</v>
+        <v>85</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>85</v>
@@ -6863,7 +6929,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -6875,7 +6941,7 @@
         <v>85</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>85</v>
@@ -6890,13 +6956,13 @@
         <v>85</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>402</v>
+        <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>403</v>
+        <v>85</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>313</v>
+        <v>138</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>85</v>
@@ -6907,10 +6973,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6933,18 +6999,16 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>85</v>
       </c>
@@ -6992,7 +7056,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7001,7 +7065,7 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>85</v>
+        <v>405</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>107</v>
@@ -7022,10 +7086,10 @@
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>85</v>
+        <v>406</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
@@ -7036,10 +7100,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7062,13 +7126,13 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7119,7 +7183,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7128,7 +7192,7 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>85</v>
+        <v>405</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>107</v>
@@ -7149,10 +7213,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -7163,10 +7227,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7177,7 +7241,7 @@
         <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>85</v>
@@ -7186,21 +7250,23 @@
         <v>85</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>422</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>85</v>
       </c>
@@ -7224,13 +7290,13 @@
         <v>85</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>85</v>
+        <v>417</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>85</v>
@@ -7248,13 +7314,13 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>85</v>
@@ -7275,13 +7341,13 @@
         <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>85</v>
+        <v>419</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>427</v>
+        <v>331</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>85</v>
@@ -7292,10 +7358,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7315,21 +7381,23 @@
         <v>85</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>429</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
       </c>
@@ -7353,13 +7421,13 @@
         <v>85</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>85</v>
+        <v>345</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>85</v>
+        <v>426</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>85</v>
+        <v>427</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>85</v>
@@ -7377,7 +7445,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7404,13 +7472,13 @@
         <v>85</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>85</v>
+        <v>419</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>433</v>
+        <v>331</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>85</v>
@@ -7421,10 +7489,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7435,7 +7503,7 @@
         <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>85</v>
@@ -7444,22 +7512,20 @@
         <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>362</v>
+        <v>429</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7508,13 +7574,13 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>85</v>
@@ -7538,10 +7604,10 @@
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>439</v>
+        <v>85</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -7552,10 +7618,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7578,13 +7644,13 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>373</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7635,7 +7701,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7647,7 +7713,7 @@
         <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>85</v>
@@ -7665,10 +7731,10 @@
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>85</v>
+        <v>406</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>375</v>
+        <v>437</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -7679,14 +7745,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7702,19 +7768,19 @@
         <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>142</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>377</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>144</v>
+        <v>442</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7764,7 +7830,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7776,7 +7842,7 @@
         <v>85</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -7794,10 +7860,10 @@
         <v>85</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>375</v>
+        <v>444</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
@@ -7808,14 +7874,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>380</v>
+        <v>85</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7828,26 +7894,24 @@
         <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>381</v>
+        <v>447</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>382</v>
+        <v>448</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>85</v>
       </c>
@@ -7895,7 +7959,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>445</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -7907,7 +7971,7 @@
         <v>85</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>85</v>
@@ -7925,10 +7989,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>138</v>
+        <v>450</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -7939,10 +8003,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7950,10 +8014,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>85</v>
@@ -7965,19 +8029,19 @@
         <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>380</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>455</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8002,13 +8066,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>327</v>
+        <v>85</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>448</v>
+        <v>85</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8026,13 +8090,13 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>85</v>
@@ -8053,16 +8117,16 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>449</v>
+        <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>218</v>
+        <v>456</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>219</v>
+        <v>457</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>85</v>
@@ -8070,10 +8134,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8093,23 +8157,19 @@
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>85</v>
       </c>
@@ -8157,7 +8217,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8169,7 +8229,7 @@
         <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>85</v>
@@ -8184,38 +8244,38 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>454</v>
+        <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>292</v>
+        <v>392</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>293</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>85</v>
@@ -8227,20 +8287,18 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>456</v>
+        <v>142</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>457</v>
+        <v>394</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>85</v>
       </c>
@@ -8264,13 +8322,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>213</v>
+        <v>85</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>459</v>
+        <v>85</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>299</v>
+        <v>85</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8288,19 +8346,19 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>455</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>85</v>
@@ -8318,10 +8376,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>302</v>
+        <v>392</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8332,14 +8390,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>304</v>
+        <v>397</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8352,25 +8410,25 @@
         <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>305</v>
+        <v>398</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>306</v>
+        <v>399</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>308</v>
+        <v>150</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8395,13 +8453,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>213</v>
+        <v>85</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8419,7 +8477,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>461</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8431,7 +8489,7 @@
         <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>85</v>
@@ -8446,27 +8504,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>311</v>
+        <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>312</v>
+        <v>85</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>313</v>
+        <v>138</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>314</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8474,10 +8532,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>85</v>
@@ -8486,22 +8544,22 @@
         <v>85</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>366</v>
+        <v>213</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -8526,13 +8584,13 @@
         <v>85</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>85</v>
+        <v>345</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>85</v>
+        <v>465</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>85</v>
@@ -8550,13 +8608,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -8577,23 +8635,547 @@
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>368</v>
+        <v>220</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>369</v>
+        <v>221</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="AS52" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AR53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS53" t="s" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AR54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS54" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AR55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS55" t="s" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AR56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS56" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS52">
+  <autoFilter ref="A1:AS56">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8603,7 +9185,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI55">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,7 +738,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>844: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1887,7 +1887,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.17578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationCytopathologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
